--- a/backend/src/main/resources/templates/alltemple_template-lead.xlsx
+++ b/backend/src/main/resources/templates/alltemple_template-lead.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="报关单" sheetId="1" r:id="rId1"/>
@@ -2061,20 +2061,20 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>250825</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>138430</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>480695</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>141605</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
+      <xdr:colOff>739140</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
+      <xdr:rowOff>149860</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2" descr="73c7f05700406c30116bf7709ac3f4b7"/>
+        <xdr:cNvPr id="2" name="图片 1" descr="73c7f05700406c30116bf7709ac3f4b7"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2087,8 +2087,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4040505" y="7342505"/>
-          <a:ext cx="1903095" cy="1652270"/>
+          <a:off x="3747135" y="6979920"/>
+          <a:ext cx="2326005" cy="2019935"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/backend/src/main/resources/templates/alltemple_template-lead.xlsx
+++ b/backend/src/main/resources/templates/alltemple_template-lead.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="1"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="报关单" sheetId="1" r:id="rId1"/>
@@ -1549,7 +1549,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1875,6 +1875,54 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="177" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1882,45 +1930,6 @@
     </xf>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3016,9 +3025,9 @@
       <c r="E22" s="80"/>
       <c r="F22" s="80"/>
       <c r="G22" s="119"/>
-      <c r="H22" s="120"/>
-      <c r="I22" s="121"/>
-      <c r="J22" s="122"/>
+      <c r="H22" s="136"/>
+      <c r="I22" s="137"/>
+      <c r="J22" s="138"/>
       <c r="K22" s="123"/>
       <c r="L22" s="119"/>
       <c r="M22" s="80"/>
@@ -3070,9 +3079,9 @@
       <c r="E25" s="80"/>
       <c r="F25" s="80"/>
       <c r="G25" s="119"/>
-      <c r="H25" s="121"/>
-      <c r="I25" s="121"/>
-      <c r="J25" s="122"/>
+      <c r="H25" s="137"/>
+      <c r="I25" s="137"/>
+      <c r="J25" s="138"/>
       <c r="K25" s="123"/>
       <c r="L25" s="119"/>
       <c r="M25" s="80"/>
@@ -3117,31 +3126,31 @@
       <c r="R27" s="125"/>
     </row>
     <row r="28" s="71" customFormat="1" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A28" s="136"/>
-      <c r="B28" s="137"/>
-      <c r="C28" s="137"/>
-      <c r="D28" s="138" t="s">
+      <c r="A28" s="139"/>
+      <c r="B28" s="140"/>
+      <c r="C28" s="140"/>
+      <c r="D28" s="141" t="s">
         <v>78</v>
       </c>
-      <c r="E28" s="137"/>
-      <c r="F28" s="137"/>
-      <c r="G28" s="137" t="s">
+      <c r="E28" s="140"/>
+      <c r="F28" s="140"/>
+      <c r="G28" s="140" t="s">
         <v>79</v>
       </c>
-      <c r="H28" s="137"/>
-      <c r="I28" s="137"/>
-      <c r="J28" s="138" t="s">
+      <c r="H28" s="140"/>
+      <c r="I28" s="140"/>
+      <c r="J28" s="141" t="s">
         <v>80</v>
       </c>
       <c r="K28" s="116"/>
       <c r="L28" s="116"/>
-      <c r="M28" s="137"/>
-      <c r="N28" s="137"/>
-      <c r="O28" s="138" t="s">
+      <c r="M28" s="140"/>
+      <c r="N28" s="140"/>
+      <c r="O28" s="141" t="s">
         <v>81</v>
       </c>
       <c r="P28" s="116"/>
-      <c r="Q28" s="139"/>
+      <c r="Q28" s="142"/>
     </row>
     <row r="29" ht="15.75" customHeight="1" spans="1:20">
       <c r="A29" s="79" t="s">
@@ -3182,25 +3191,25 @@
       <c r="K30" s="87"/>
       <c r="L30" s="87"/>
       <c r="M30" s="96"/>
-      <c r="Q30" s="140"/>
+      <c r="Q30" s="143"/>
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A31" s="141" t="s">
+      <c r="A31" s="144" t="s">
         <v>85</v>
       </c>
       <c r="B31" s="78"/>
-      <c r="C31" s="142"/>
+      <c r="C31" s="145"/>
       <c r="D31" s="78"/>
       <c r="E31" s="78"/>
       <c r="F31" s="78"/>
       <c r="G31" s="78"/>
-      <c r="H31" s="143"/>
-      <c r="I31" s="143"/>
-      <c r="J31" s="142" t="s">
+      <c r="H31" s="146"/>
+      <c r="I31" s="146"/>
+      <c r="J31" s="145" t="s">
         <v>86</v>
       </c>
       <c r="K31" s="78"/>
-      <c r="L31" s="143"/>
+      <c r="L31" s="146"/>
       <c r="M31" s="102"/>
       <c r="N31" s="78"/>
       <c r="O31" s="78"/>
@@ -3208,7 +3217,7 @@
       <c r="Q31" s="97"/>
     </row>
     <row r="32" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A32" s="144" t="s">
+      <c r="A32" s="147" t="s">
         <v>87</v>
       </c>
       <c r="B32" s="80"/>

--- a/backend/src/main/resources/templates/alltemple_template-lead.xlsx
+++ b/backend/src/main/resources/templates/alltemple_template-lead.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="报关单" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="136">
   <si>
     <t>中华人民共和国海关进口货物报关单</t>
   </si>
@@ -345,11 +345,10 @@
     <t>Amount</t>
   </si>
   <si>
-    <t>FOB SHANGHAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHINA
-    </t>
+    <t>{tradeTerm} {port}</t>
+  </si>
+  <si>
+    <t>{currency}</t>
   </si>
   <si>
     <t>{.productName}</t>
@@ -365,9 +364,6 @@
   </si>
   <si>
     <t xml:space="preserve">      TOTAL:</t>
-  </si>
-  <si>
-    <t>{currency}</t>
   </si>
   <si>
     <t>{totalAmount}</t>
@@ -1705,7 +1701,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3558,27 +3554,27 @@
       <c r="D17" s="56"/>
       <c r="E17" s="56"/>
       <c r="F17" s="65" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" s="67" t="s">
         <v>110</v>
-      </c>
-      <c r="G17" s="67" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="18" ht="21.95" customHeight="1" spans="1:7">
       <c r="A18" s="68" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G18" s="8"/>
     </row>
     <row r="19" ht="21.95" customHeight="1" spans="1:7">
       <c r="A19" s="68" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G19" s="8"/>
     </row>
     <row r="20" ht="21.95" customHeight="1" spans="1:7">
       <c r="A20" s="69" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G20" s="8"/>
     </row>
@@ -3680,10 +3676,10 @@
   <sheetData>
     <row r="1" ht="47.45" customHeight="1" spans="1:16">
       <c r="A1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -3729,7 +3725,7 @@
       <c r="D4" s="16"/>
       <c r="E4" s="17"/>
       <c r="F4" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="16"/>
@@ -3739,10 +3735,10 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:16">
       <c r="A5" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>118</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>119</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -3785,19 +3781,19 @@
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G8" s="17"/>
       <c r="H8" s="24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K8" s="17"/>
     </row>
@@ -3812,28 +3808,28 @@
         <v>107</v>
       </c>
       <c r="D9" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="F9" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="G9" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="H9" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="I9" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="J9" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="I9" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="J9" s="29" t="s">
+      <c r="K9" s="30" t="s">
         <v>129</v>
-      </c>
-      <c r="K9" s="30" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="10" ht="21.95" customHeight="1" spans="1:16">
@@ -3937,30 +3933,30 @@
         <v>44</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F17" s="43" t="s">
         <v>45</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H17" s="43" t="s">
         <v>46</v>
       </c>
       <c r="I17" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="J17" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="J17" s="43" t="s">
+      <c r="K17" s="44" t="s">
         <v>133</v>
-      </c>
-      <c r="K17" s="44" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="18" ht="21.95" customHeight="1" spans="1:11">
       <c r="A18" s="45" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B18" s="46"/>
       <c r="C18" s="46"/>
@@ -3975,7 +3971,7 @@
     </row>
     <row r="19" ht="21.95" customHeight="1" spans="1:11">
       <c r="A19" s="48" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K19" s="8"/>
     </row>

--- a/backend/src/main/resources/templates/alltemple_template-lead.xlsx
+++ b/backend/src/main/resources/templates/alltemple_template-lead.xlsx
@@ -46,7 +46,7 @@
     <t>海关编号：{customsNo}</t>
   </si>
   <si>
-    <t>境内发货人 3302968B3G</t>
+    <t>境内发货人 3302968DGP</t>
   </si>
   <si>
     <t>出境关别</t>
@@ -376,12 +376,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
       <t>ACCOUNT NAME</t>
     </r>
     <r>
@@ -400,7 +394,8 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>NINGBO LIDE TECHNOLOGY CO.,LTD.                                                                                                  ADDRESS</t>
+      <t>NINGBO LIDE TECHNOLOGY CO.,LTD.                                                                                                  
+ADDRESS</t>
     </r>
     <r>
       <rPr>
@@ -418,7 +413,9 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>Xiufeng, Gaoqiao Town, Haishu District, Ningbo, Zhejiang                                                                                               BANK NAME : BANK OF CHINA , NINGBO GAOQIAO SUB-BRANCH                                                                             BANK ADDRESS</t>
+      <t>Xiufeng, Gaoqiao Town, Haishu District, Ningbo, Zhejiang                                                                                               
+BANK NAME : BANK OF CHINA , NINGBO GAOQIAO SUB-BRANCH                                                                             
+BANK ADDRESS</t>
     </r>
     <r>
       <rPr>
@@ -436,7 +433,8 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">221, 223 LIAN FENG ZHONG ROAD, NINGBO CITY, ZHEJIANG, CHINA                                                BANK ACCOUNT NO.: 402686490492
+      <t xml:space="preserve">221, 223 LIAN FENG ZHONG ROAD, NINGBO CITY, ZHEJIANG, CHINA                                                
+BANK ACCOUNT NO.: 402686490492
 SWIFT CODE: BKCHCNBJ92A       </t>
     </r>
   </si>
@@ -1545,7 +1543,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1735,6 +1733,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2066,16 +2082,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>480695</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>141605</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>3231515</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>133985</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>739140</xdr:colOff>
+      <xdr:colOff>223520</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>149860</xdr:rowOff>
+      <xdr:rowOff>508000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2092,7 +2108,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3747135" y="6979920"/>
+          <a:off x="3231515" y="7338060"/>
           <a:ext cx="2326005" cy="2019935"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2438,800 +2454,800 @@
   <dimension ref="A1:T32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.3796296296296" style="74" customWidth="1"/>
-    <col min="2" max="2" width="8.87962962962963" style="74" customWidth="1"/>
-    <col min="3" max="3" width="11.1111111111111" style="74" customWidth="1"/>
-    <col min="4" max="4" width="4.44444444444444" style="74" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6296296296296" style="74" customWidth="1"/>
-    <col min="6" max="6" width="13" style="74" customWidth="1"/>
-    <col min="7" max="7" width="9.77777777777778" style="74" customWidth="1"/>
-    <col min="8" max="8" width="11.6296296296296" style="74" customWidth="1"/>
-    <col min="9" max="9" width="10" style="74" customWidth="1"/>
-    <col min="10" max="10" width="4.62962962962963" style="74" customWidth="1"/>
-    <col min="11" max="11" width="16.3333333333333" style="74" customWidth="1"/>
-    <col min="12" max="12" width="6.5" style="74" customWidth="1"/>
-    <col min="13" max="13" width="8.77777777777778" style="74" customWidth="1"/>
-    <col min="14" max="14" width="3.87962962962963" style="74" customWidth="1"/>
-    <col min="15" max="15" width="6.75" style="74" customWidth="1"/>
-    <col min="16" max="16" width="6.66666666666667" style="74" customWidth="1"/>
-    <col min="17" max="17" width="18.6666666666667" style="74" customWidth="1"/>
-    <col min="18" max="19" width="9" style="74" customWidth="1"/>
-    <col min="20" max="20" width="12.75" style="74" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="74" customWidth="1"/>
+    <col min="1" max="1" width="14.3796296296296" style="80" customWidth="1"/>
+    <col min="2" max="2" width="8.87962962962963" style="80" customWidth="1"/>
+    <col min="3" max="3" width="11.1111111111111" style="80" customWidth="1"/>
+    <col min="4" max="4" width="4.44444444444444" style="80" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6296296296296" style="80" customWidth="1"/>
+    <col min="6" max="6" width="13" style="80" customWidth="1"/>
+    <col min="7" max="7" width="9.77777777777778" style="80" customWidth="1"/>
+    <col min="8" max="8" width="11.6296296296296" style="80" customWidth="1"/>
+    <col min="9" max="9" width="10" style="80" customWidth="1"/>
+    <col min="10" max="10" width="4.62962962962963" style="80" customWidth="1"/>
+    <col min="11" max="11" width="16.3333333333333" style="80" customWidth="1"/>
+    <col min="12" max="12" width="6.5" style="80" customWidth="1"/>
+    <col min="13" max="13" width="8.77777777777778" style="80" customWidth="1"/>
+    <col min="14" max="14" width="3.87962962962963" style="80" customWidth="1"/>
+    <col min="15" max="15" width="6.75" style="80" customWidth="1"/>
+    <col min="16" max="16" width="6.66666666666667" style="80" customWidth="1"/>
+    <col min="17" max="17" width="18.6666666666667" style="80" customWidth="1"/>
+    <col min="18" max="19" width="9" style="80" customWidth="1"/>
+    <col min="20" max="20" width="12.75" style="80" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="80" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="53.25" customHeight="1" spans="1:20">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="S1" s="74" t="s">
+      <c r="S1" s="80" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" s="70" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A2" s="76" t="s">
+    <row r="2" s="76" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A2" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="70" t="s">
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="77"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="78"/>
-    </row>
-    <row r="3" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A3" s="79" t="s">
+      <c r="F2" s="83"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
+    </row>
+    <row r="3" s="77" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A3" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="81" t="s">
+      <c r="B3" s="86"/>
+      <c r="C3" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="82"/>
-      <c r="E3" s="83" t="s">
+      <c r="D3" s="88"/>
+      <c r="E3" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="84"/>
-      <c r="G3" s="85" t="s">
+      <c r="F3" s="90"/>
+      <c r="G3" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="79" t="s">
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="85" t="s">
+      <c r="L3" s="86"/>
+      <c r="M3" s="86"/>
+      <c r="N3" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="80"/>
-      <c r="P3" s="80"/>
-      <c r="Q3" s="82"/>
-    </row>
-    <row r="4" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A4" s="86" t="s">
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="88"/>
+    </row>
+    <row r="4" s="77" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A4" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="87"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="86" t="s">
+      <c r="B4" s="93"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="92"/>
-      <c r="K4" s="86" t="s">
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="87"/>
-      <c r="M4" s="87"/>
-      <c r="N4" s="86" t="s">
+      <c r="L4" s="93"/>
+      <c r="M4" s="93"/>
+      <c r="N4" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="87"/>
-      <c r="P4" s="87"/>
-      <c r="Q4" s="92"/>
+      <c r="O4" s="93"/>
+      <c r="P4" s="93"/>
+      <c r="Q4" s="98"/>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:20">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="97"/>
-      <c r="K5" s="93"/>
-      <c r="L5" s="78"/>
-      <c r="M5" s="78"/>
-      <c r="N5" s="96"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="97"/>
-    </row>
-    <row r="6" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A6" s="79" t="s">
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="102"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="99"/>
+      <c r="L5" s="84"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="102"/>
+      <c r="O5" s="84"/>
+      <c r="P5" s="84"/>
+      <c r="Q5" s="103"/>
+    </row>
+    <row r="6" s="77" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A6" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="80"/>
-      <c r="C6" s="81"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="83" t="s">
+      <c r="B6" s="86"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="84"/>
-      <c r="G6" s="85" t="s">
+      <c r="F6" s="90"/>
+      <c r="G6" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="98" t="s">
+      <c r="H6" s="86"/>
+      <c r="I6" s="86"/>
+      <c r="J6" s="88"/>
+      <c r="K6" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
-      <c r="P6" s="80"/>
-      <c r="Q6" s="82"/>
+      <c r="L6" s="86"/>
+      <c r="M6" s="86"/>
+      <c r="N6" s="86"/>
+      <c r="O6" s="86"/>
+      <c r="P6" s="86"/>
+      <c r="Q6" s="88"/>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:20">
-      <c r="A7" s="99" t="s">
+      <c r="A7" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="100"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="96" t="s">
+      <c r="B7" s="106"/>
+      <c r="C7" s="106"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="97"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="78"/>
-      <c r="I7" s="78"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="78"/>
-      <c r="M7" s="78"/>
-      <c r="N7" s="78"/>
-      <c r="O7" s="78"/>
-      <c r="P7" s="78"/>
-      <c r="Q7" s="97"/>
-    </row>
-    <row r="8" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A8" s="79" t="s">
+      <c r="F7" s="103"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="103"/>
+      <c r="K7" s="108"/>
+      <c r="L7" s="84"/>
+      <c r="M7" s="84"/>
+      <c r="N7" s="84"/>
+      <c r="O7" s="84"/>
+      <c r="P7" s="84"/>
+      <c r="Q7" s="103"/>
+    </row>
+    <row r="8" s="77" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A8" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="80"/>
-      <c r="C8" s="81"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="83" t="s">
+      <c r="B8" s="86"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="103"/>
-      <c r="G8" s="79" t="s">
+      <c r="F8" s="109"/>
+      <c r="G8" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="80"/>
-      <c r="I8" s="103"/>
-      <c r="J8" s="82"/>
-      <c r="K8" s="98" t="s">
+      <c r="H8" s="86"/>
+      <c r="I8" s="109"/>
+      <c r="J8" s="88"/>
+      <c r="K8" s="104" t="s">
         <v>23</v>
       </c>
-      <c r="L8" s="80"/>
-      <c r="M8" s="80"/>
-      <c r="N8" s="80"/>
-      <c r="O8" s="80"/>
-      <c r="P8" s="80"/>
-      <c r="Q8" s="82"/>
-      <c r="T8" s="74"/>
+      <c r="L8" s="86"/>
+      <c r="M8" s="86"/>
+      <c r="N8" s="86"/>
+      <c r="O8" s="86"/>
+      <c r="P8" s="86"/>
+      <c r="Q8" s="88"/>
+      <c r="T8" s="80"/>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:20">
-      <c r="A9" s="96" t="s">
+      <c r="A9" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="78"/>
-      <c r="C9" s="78"/>
-      <c r="D9" s="97"/>
-      <c r="E9" s="104" t="s">
+      <c r="B9" s="84"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="103"/>
+      <c r="E9" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="97"/>
-      <c r="G9" s="104" t="s">
+      <c r="F9" s="103"/>
+      <c r="G9" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
-      <c r="J9" s="97"/>
-      <c r="K9" s="102"/>
-      <c r="L9" s="78"/>
-      <c r="M9" s="78"/>
-      <c r="N9" s="78"/>
-      <c r="O9" s="78"/>
-      <c r="P9" s="78"/>
-      <c r="Q9" s="97"/>
-    </row>
-    <row r="10" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A10" s="79" t="s">
+      <c r="H9" s="84"/>
+      <c r="I9" s="84"/>
+      <c r="J9" s="103"/>
+      <c r="K9" s="108"/>
+      <c r="L9" s="84"/>
+      <c r="M9" s="84"/>
+      <c r="N9" s="84"/>
+      <c r="O9" s="84"/>
+      <c r="P9" s="84"/>
+      <c r="Q9" s="103"/>
+    </row>
+    <row r="10" s="77" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A10" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="80"/>
-      <c r="C10" s="81"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="83" t="s">
+      <c r="B10" s="86"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="84"/>
-      <c r="G10" s="79" t="s">
+      <c r="F10" s="90"/>
+      <c r="G10" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="80"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="82"/>
-      <c r="K10" s="79" t="s">
+      <c r="H10" s="86"/>
+      <c r="I10" s="87"/>
+      <c r="J10" s="88"/>
+      <c r="K10" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="81" t="s">
+      <c r="L10" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="M10" s="82"/>
-      <c r="N10" s="79" t="s">
+      <c r="M10" s="88"/>
+      <c r="N10" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="O10" s="80"/>
-      <c r="P10" s="81" t="s">
+      <c r="O10" s="86"/>
+      <c r="P10" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="Q10" s="82"/>
-      <c r="T10" s="74"/>
+      <c r="Q10" s="88"/>
+      <c r="T10" s="80"/>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:20">
-      <c r="A11" s="96" t="s">
+      <c r="A11" s="102" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="96" t="s">
+      <c r="B11" s="84"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="103"/>
+      <c r="E11" s="102" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="101"/>
-      <c r="G11" s="96" t="s">
+      <c r="F11" s="107"/>
+      <c r="G11" s="102" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="100"/>
-      <c r="I11" s="100"/>
-      <c r="J11" s="101"/>
-      <c r="K11" s="96" t="s">
+      <c r="H11" s="106"/>
+      <c r="I11" s="106"/>
+      <c r="J11" s="107"/>
+      <c r="K11" s="102" t="s">
         <v>33</v>
       </c>
-      <c r="L11" s="78"/>
-      <c r="M11" s="97"/>
-      <c r="N11" s="96" t="s">
+      <c r="L11" s="84"/>
+      <c r="M11" s="103"/>
+      <c r="N11" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="O11" s="78"/>
-      <c r="P11" s="78"/>
-      <c r="Q11" s="97"/>
-    </row>
-    <row r="12" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A12" s="79" t="s">
+      <c r="O11" s="84"/>
+      <c r="P11" s="84"/>
+      <c r="Q11" s="103"/>
+    </row>
+    <row r="12" s="77" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A12" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="80"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="105" t="s">
+      <c r="B12" s="86"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="88"/>
+      <c r="E12" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="105" t="s">
+      <c r="F12" s="111" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="85" t="s">
+      <c r="G12" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="H12" s="82"/>
-      <c r="I12" s="79" t="s">
+      <c r="H12" s="88"/>
+      <c r="I12" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="J12" s="106"/>
-      <c r="K12" s="79" t="s">
+      <c r="J12" s="112"/>
+      <c r="K12" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="L12" s="80"/>
-      <c r="M12" s="85" t="s">
+      <c r="L12" s="86"/>
+      <c r="M12" s="91" t="s">
         <v>41</v>
       </c>
-      <c r="N12" s="80"/>
-      <c r="O12" s="82"/>
-      <c r="P12" s="85" t="s">
+      <c r="N12" s="86"/>
+      <c r="O12" s="88"/>
+      <c r="P12" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="Q12" s="82"/>
-      <c r="T12" s="74"/>
+      <c r="Q12" s="88"/>
+      <c r="T12" s="80"/>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:20">
-      <c r="A13" s="96" t="s">
+      <c r="A13" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="78"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="96" t="s">
+      <c r="B13" s="84"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="102" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="96" t="s">
+      <c r="F13" s="102" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="96" t="s">
+      <c r="G13" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="97"/>
-      <c r="I13" s="107" t="s">
+      <c r="H13" s="103"/>
+      <c r="I13" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="J13" s="95"/>
-      <c r="K13" s="108" t="s">
+      <c r="J13" s="101"/>
+      <c r="K13" s="114" t="s">
         <v>48</v>
       </c>
-      <c r="L13" s="78"/>
-      <c r="M13" s="96" t="s">
+      <c r="L13" s="84"/>
+      <c r="M13" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="N13" s="78"/>
-      <c r="O13" s="97"/>
-      <c r="P13" s="96" t="s">
+      <c r="N13" s="84"/>
+      <c r="O13" s="103"/>
+      <c r="P13" s="102" t="s">
         <v>50</v>
       </c>
-      <c r="Q13" s="97"/>
-    </row>
-    <row r="14" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A14" s="85" t="s">
+      <c r="Q13" s="103"/>
+    </row>
+    <row r="14" s="77" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A14" s="91" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="80"/>
-      <c r="C14" s="80"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="80"/>
-      <c r="G14" s="80"/>
-      <c r="H14" s="80"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="80"/>
-      <c r="K14" s="80"/>
-      <c r="L14" s="80"/>
-      <c r="M14" s="80"/>
-      <c r="N14" s="80"/>
-      <c r="O14" s="80"/>
-      <c r="P14" s="80"/>
-      <c r="Q14" s="82"/>
-      <c r="T14" s="74"/>
-    </row>
-    <row r="15" s="72" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A15" s="109" t="s">
+      <c r="B14" s="86"/>
+      <c r="C14" s="86"/>
+      <c r="D14" s="86"/>
+      <c r="E14" s="86"/>
+      <c r="F14" s="86"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="86"/>
+      <c r="I14" s="86"/>
+      <c r="J14" s="86"/>
+      <c r="K14" s="86"/>
+      <c r="L14" s="86"/>
+      <c r="M14" s="86"/>
+      <c r="N14" s="86"/>
+      <c r="O14" s="86"/>
+      <c r="P14" s="86"/>
+      <c r="Q14" s="88"/>
+      <c r="T14" s="80"/>
+    </row>
+    <row r="15" s="78" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A15" s="115" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="78"/>
-      <c r="C15" s="78"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="110" t="s">
+      <c r="B15" s="84"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="116" t="s">
         <v>53</v>
       </c>
-      <c r="I15" s="78"/>
-      <c r="J15" s="78"/>
-      <c r="K15" s="78"/>
-      <c r="L15" s="78"/>
-      <c r="M15" s="78"/>
-      <c r="N15" s="78"/>
-      <c r="O15" s="78"/>
-      <c r="P15" s="78"/>
-      <c r="Q15" s="97"/>
-      <c r="T15" s="74"/>
-    </row>
-    <row r="16" s="71" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A16" s="83" t="s">
+      <c r="I15" s="84"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="84"/>
+      <c r="N15" s="84"/>
+      <c r="O15" s="84"/>
+      <c r="P15" s="84"/>
+      <c r="Q15" s="103"/>
+      <c r="T15" s="80"/>
+    </row>
+    <row r="16" s="77" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A16" s="89" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="111"/>
-      <c r="C16" s="112"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="111"/>
-      <c r="L16" s="111"/>
-      <c r="M16" s="111"/>
-      <c r="N16" s="111"/>
-      <c r="O16" s="111"/>
-      <c r="P16" s="111"/>
-      <c r="Q16" s="113"/>
-      <c r="T16" s="74"/>
+      <c r="B16" s="117"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="117"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="117"/>
+      <c r="G16" s="117"/>
+      <c r="H16" s="117"/>
+      <c r="I16" s="117"/>
+      <c r="J16" s="117"/>
+      <c r="K16" s="117"/>
+      <c r="L16" s="117"/>
+      <c r="M16" s="117"/>
+      <c r="N16" s="117"/>
+      <c r="O16" s="117"/>
+      <c r="P16" s="117"/>
+      <c r="Q16" s="119"/>
+      <c r="T16" s="80"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A17" s="96" t="s">
+      <c r="A17" s="102" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="78"/>
-      <c r="J17" s="78"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="78"/>
-      <c r="M17" s="78"/>
-      <c r="N17" s="78"/>
-      <c r="O17" s="78"/>
-      <c r="P17" s="78"/>
-      <c r="Q17" s="97"/>
-    </row>
-    <row r="18" s="73" customFormat="1" ht="18.75" customHeight="1" spans="1:20">
-      <c r="A18" s="114" t="s">
+      <c r="B17" s="84"/>
+      <c r="C17" s="84"/>
+      <c r="D17" s="84"/>
+      <c r="E17" s="84"/>
+      <c r="F17" s="84"/>
+      <c r="G17" s="84"/>
+      <c r="H17" s="84"/>
+      <c r="I17" s="84"/>
+      <c r="J17" s="84"/>
+      <c r="K17" s="84"/>
+      <c r="L17" s="84"/>
+      <c r="M17" s="84"/>
+      <c r="N17" s="84"/>
+      <c r="O17" s="84"/>
+      <c r="P17" s="84"/>
+      <c r="Q17" s="103"/>
+    </row>
+    <row r="18" s="79" customFormat="1" ht="18.75" customHeight="1" spans="1:20">
+      <c r="A18" s="120" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="115" t="s">
+      <c r="B18" s="121" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="116"/>
-      <c r="D18" s="115" t="s">
+      <c r="C18" s="122"/>
+      <c r="D18" s="121" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="115" t="s">
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="121" t="s">
         <v>59</v>
       </c>
-      <c r="H18" s="115" t="s">
+      <c r="H18" s="121" t="s">
         <v>60</v>
       </c>
-      <c r="I18" s="116"/>
-      <c r="J18" s="116"/>
-      <c r="K18" s="115" t="s">
+      <c r="I18" s="122"/>
+      <c r="J18" s="122"/>
+      <c r="K18" s="121" t="s">
         <v>61</v>
       </c>
-      <c r="L18" s="115" t="s">
+      <c r="L18" s="121" t="s">
         <v>62</v>
       </c>
-      <c r="M18" s="116"/>
-      <c r="N18" s="115" t="s">
+      <c r="M18" s="122"/>
+      <c r="N18" s="121" t="s">
         <v>63</v>
       </c>
-      <c r="O18" s="116"/>
-      <c r="P18" s="116"/>
-      <c r="Q18" s="117" t="s">
+      <c r="O18" s="122"/>
+      <c r="P18" s="122"/>
+      <c r="Q18" s="123" t="s">
         <v>64</v>
       </c>
-      <c r="T18" s="74"/>
-    </row>
-    <row r="19" s="74" customFormat="1" spans="1:20">
-      <c r="A19" s="118" t="s">
+      <c r="T18" s="80"/>
+    </row>
+    <row r="19" s="80" customFormat="1" spans="1:20">
+      <c r="A19" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="119" t="s">
+      <c r="B19" s="125" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="80"/>
-      <c r="D19" s="119" t="s">
+      <c r="C19" s="86"/>
+      <c r="D19" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="80"/>
-      <c r="F19" s="80"/>
-      <c r="G19" s="119" t="s">
+      <c r="E19" s="86"/>
+      <c r="F19" s="86"/>
+      <c r="G19" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="H19" s="120" t="s">
+      <c r="H19" s="126" t="s">
         <v>69</v>
       </c>
-      <c r="I19" s="121" t="s">
+      <c r="I19" s="127" t="s">
         <v>70</v>
       </c>
-      <c r="J19" s="122" t="s">
+      <c r="J19" s="128" t="s">
         <v>71</v>
       </c>
-      <c r="K19" s="123" t="s">
+      <c r="K19" s="129" t="s">
         <v>72</v>
       </c>
-      <c r="L19" s="119" t="s">
+      <c r="L19" s="125" t="s">
         <v>73</v>
       </c>
-      <c r="M19" s="80"/>
-      <c r="N19" s="119" t="s">
+      <c r="M19" s="86"/>
+      <c r="N19" s="125" t="s">
         <v>74</v>
       </c>
-      <c r="O19" s="80"/>
-      <c r="P19" s="80"/>
-      <c r="Q19" s="124" t="s">
+      <c r="O19" s="86"/>
+      <c r="P19" s="86"/>
+      <c r="Q19" s="130" t="s">
         <v>75</v>
       </c>
-      <c r="R19" s="125"/>
-    </row>
-    <row r="20" s="74" customFormat="1" spans="1:20">
-      <c r="A20" s="126"/>
-      <c r="B20" s="127"/>
-      <c r="C20" s="127"/>
-      <c r="D20" s="128" t="s">
+      <c r="R19" s="131"/>
+    </row>
+    <row r="20" s="80" customFormat="1" spans="1:20">
+      <c r="A20" s="132"/>
+      <c r="B20" s="133"/>
+      <c r="C20" s="133"/>
+      <c r="D20" s="134" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="128"/>
-      <c r="F20" s="128"/>
-      <c r="G20" s="129" t="s">
+      <c r="E20" s="134"/>
+      <c r="F20" s="134"/>
+      <c r="G20" s="135" t="s">
         <v>77</v>
       </c>
-      <c r="H20" s="130"/>
-      <c r="I20" s="130"/>
-      <c r="J20" s="131"/>
-      <c r="K20" s="132"/>
-      <c r="L20" s="127"/>
-      <c r="M20" s="127"/>
-      <c r="N20" s="127"/>
-      <c r="O20" s="127"/>
-      <c r="P20" s="127"/>
-      <c r="Q20" s="133"/>
-      <c r="R20" s="125"/>
-    </row>
-    <row r="21" s="74" customFormat="1" ht="39" customHeight="1" spans="1:20">
-      <c r="A21" s="126"/>
-      <c r="B21" s="127"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="128"/>
-      <c r="F21" s="128"/>
-      <c r="G21" s="129"/>
-      <c r="H21" s="134"/>
-      <c r="K21" s="135"/>
-      <c r="L21" s="127"/>
-      <c r="N21" s="127"/>
-      <c r="Q21" s="133"/>
-      <c r="R21" s="125"/>
-    </row>
-    <row r="22" s="74" customFormat="1" spans="1:20">
-      <c r="A22" s="118"/>
-      <c r="B22" s="119"/>
-      <c r="C22" s="80"/>
-      <c r="D22" s="119"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="80"/>
-      <c r="G22" s="119"/>
-      <c r="H22" s="136"/>
-      <c r="I22" s="137"/>
-      <c r="J22" s="138"/>
-      <c r="K22" s="123"/>
-      <c r="L22" s="119"/>
-      <c r="M22" s="80"/>
-      <c r="N22" s="119"/>
-      <c r="O22" s="80"/>
-      <c r="P22" s="80"/>
-      <c r="Q22" s="124"/>
-      <c r="R22" s="125"/>
-    </row>
-    <row r="23" s="74" customFormat="1" spans="1:20">
-      <c r="A23" s="126"/>
-      <c r="B23" s="127"/>
-      <c r="C23" s="127"/>
-      <c r="D23" s="128"/>
-      <c r="E23" s="128"/>
-      <c r="F23" s="128"/>
-      <c r="G23" s="129"/>
-      <c r="H23" s="130"/>
-      <c r="I23" s="130"/>
-      <c r="J23" s="131"/>
-      <c r="K23" s="132"/>
-      <c r="L23" s="127"/>
-      <c r="M23" s="127"/>
-      <c r="N23" s="127"/>
-      <c r="O23" s="127"/>
-      <c r="P23" s="127"/>
-      <c r="Q23" s="133"/>
-      <c r="R23" s="125"/>
-    </row>
-    <row r="24" s="74" customFormat="1" ht="40" customHeight="1" spans="1:20">
-      <c r="A24" s="126"/>
-      <c r="B24" s="127"/>
-      <c r="D24" s="128"/>
-      <c r="E24" s="128"/>
-      <c r="F24" s="128"/>
-      <c r="G24" s="129"/>
-      <c r="H24" s="134"/>
-      <c r="K24" s="135"/>
-      <c r="L24" s="127"/>
-      <c r="N24" s="127"/>
-      <c r="Q24" s="133"/>
-      <c r="R24" s="125"/>
-    </row>
-    <row r="25" s="74" customFormat="1" spans="1:20">
-      <c r="A25" s="118"/>
-      <c r="B25" s="119"/>
-      <c r="C25" s="80"/>
-      <c r="D25" s="119"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="80"/>
-      <c r="G25" s="119"/>
-      <c r="H25" s="137"/>
-      <c r="I25" s="137"/>
-      <c r="J25" s="138"/>
-      <c r="K25" s="123"/>
-      <c r="L25" s="119"/>
-      <c r="M25" s="80"/>
-      <c r="N25" s="119"/>
-      <c r="O25" s="80"/>
-      <c r="P25" s="80"/>
-      <c r="Q25" s="124"/>
-      <c r="R25" s="125"/>
-    </row>
-    <row r="26" s="74" customFormat="1" spans="1:20">
-      <c r="A26" s="126"/>
-      <c r="B26" s="127"/>
-      <c r="C26" s="127"/>
-      <c r="D26" s="128"/>
-      <c r="E26" s="128"/>
-      <c r="F26" s="128"/>
-      <c r="G26" s="129"/>
-      <c r="H26" s="130"/>
-      <c r="I26" s="130"/>
-      <c r="J26" s="131"/>
-      <c r="K26" s="132"/>
-      <c r="L26" s="127"/>
-      <c r="M26" s="127"/>
-      <c r="N26" s="127"/>
-      <c r="O26" s="127"/>
-      <c r="P26" s="127"/>
-      <c r="Q26" s="133"/>
-      <c r="R26" s="125"/>
-    </row>
-    <row r="27" s="74" customFormat="1" ht="42" customHeight="1" spans="1:20">
-      <c r="A27" s="126"/>
-      <c r="B27" s="127"/>
-      <c r="D27" s="128"/>
-      <c r="E27" s="128"/>
-      <c r="F27" s="128"/>
-      <c r="G27" s="129"/>
-      <c r="H27" s="134"/>
-      <c r="K27" s="135"/>
-      <c r="L27" s="127"/>
-      <c r="N27" s="127"/>
-      <c r="Q27" s="133"/>
-      <c r="R27" s="125"/>
-    </row>
-    <row r="28" s="71" customFormat="1" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A28" s="139"/>
-      <c r="B28" s="140"/>
-      <c r="C28" s="140"/>
-      <c r="D28" s="141" t="s">
+      <c r="H20" s="136"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="137"/>
+      <c r="K20" s="138"/>
+      <c r="L20" s="133"/>
+      <c r="M20" s="133"/>
+      <c r="N20" s="133"/>
+      <c r="O20" s="133"/>
+      <c r="P20" s="133"/>
+      <c r="Q20" s="139"/>
+      <c r="R20" s="131"/>
+    </row>
+    <row r="21" s="80" customFormat="1" ht="39" customHeight="1" spans="1:20">
+      <c r="A21" s="132"/>
+      <c r="B21" s="133"/>
+      <c r="D21" s="134"/>
+      <c r="E21" s="134"/>
+      <c r="F21" s="134"/>
+      <c r="G21" s="135"/>
+      <c r="H21" s="140"/>
+      <c r="K21" s="141"/>
+      <c r="L21" s="133"/>
+      <c r="N21" s="133"/>
+      <c r="Q21" s="139"/>
+      <c r="R21" s="131"/>
+    </row>
+    <row r="22" s="80" customFormat="1" spans="1:20">
+      <c r="A22" s="124"/>
+      <c r="B22" s="125"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="125"/>
+      <c r="E22" s="86"/>
+      <c r="F22" s="86"/>
+      <c r="G22" s="125"/>
+      <c r="H22" s="142"/>
+      <c r="I22" s="143"/>
+      <c r="J22" s="144"/>
+      <c r="K22" s="129"/>
+      <c r="L22" s="125"/>
+      <c r="M22" s="86"/>
+      <c r="N22" s="125"/>
+      <c r="O22" s="86"/>
+      <c r="P22" s="86"/>
+      <c r="Q22" s="130"/>
+      <c r="R22" s="131"/>
+    </row>
+    <row r="23" s="80" customFormat="1" spans="1:20">
+      <c r="A23" s="132"/>
+      <c r="B23" s="133"/>
+      <c r="C23" s="133"/>
+      <c r="D23" s="134"/>
+      <c r="E23" s="134"/>
+      <c r="F23" s="134"/>
+      <c r="G23" s="135"/>
+      <c r="H23" s="136"/>
+      <c r="I23" s="136"/>
+      <c r="J23" s="137"/>
+      <c r="K23" s="138"/>
+      <c r="L23" s="133"/>
+      <c r="M23" s="133"/>
+      <c r="N23" s="133"/>
+      <c r="O23" s="133"/>
+      <c r="P23" s="133"/>
+      <c r="Q23" s="139"/>
+      <c r="R23" s="131"/>
+    </row>
+    <row r="24" s="80" customFormat="1" ht="40" customHeight="1" spans="1:20">
+      <c r="A24" s="132"/>
+      <c r="B24" s="133"/>
+      <c r="D24" s="134"/>
+      <c r="E24" s="134"/>
+      <c r="F24" s="134"/>
+      <c r="G24" s="135"/>
+      <c r="H24" s="140"/>
+      <c r="K24" s="141"/>
+      <c r="L24" s="133"/>
+      <c r="N24" s="133"/>
+      <c r="Q24" s="139"/>
+      <c r="R24" s="131"/>
+    </row>
+    <row r="25" s="80" customFormat="1" spans="1:20">
+      <c r="A25" s="124"/>
+      <c r="B25" s="125"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="125"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="125"/>
+      <c r="H25" s="143"/>
+      <c r="I25" s="143"/>
+      <c r="J25" s="144"/>
+      <c r="K25" s="129"/>
+      <c r="L25" s="125"/>
+      <c r="M25" s="86"/>
+      <c r="N25" s="125"/>
+      <c r="O25" s="86"/>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="130"/>
+      <c r="R25" s="131"/>
+    </row>
+    <row r="26" s="80" customFormat="1" spans="1:20">
+      <c r="A26" s="132"/>
+      <c r="B26" s="133"/>
+      <c r="C26" s="133"/>
+      <c r="D26" s="134"/>
+      <c r="E26" s="134"/>
+      <c r="F26" s="134"/>
+      <c r="G26" s="135"/>
+      <c r="H26" s="136"/>
+      <c r="I26" s="136"/>
+      <c r="J26" s="137"/>
+      <c r="K26" s="138"/>
+      <c r="L26" s="133"/>
+      <c r="M26" s="133"/>
+      <c r="N26" s="133"/>
+      <c r="O26" s="133"/>
+      <c r="P26" s="133"/>
+      <c r="Q26" s="139"/>
+      <c r="R26" s="131"/>
+    </row>
+    <row r="27" s="80" customFormat="1" ht="42" customHeight="1" spans="1:20">
+      <c r="A27" s="132"/>
+      <c r="B27" s="133"/>
+      <c r="D27" s="134"/>
+      <c r="E27" s="134"/>
+      <c r="F27" s="134"/>
+      <c r="G27" s="135"/>
+      <c r="H27" s="140"/>
+      <c r="K27" s="141"/>
+      <c r="L27" s="133"/>
+      <c r="N27" s="133"/>
+      <c r="Q27" s="139"/>
+      <c r="R27" s="131"/>
+    </row>
+    <row r="28" s="77" customFormat="1" ht="16.5" customHeight="1" spans="1:20">
+      <c r="A28" s="145"/>
+      <c r="B28" s="146"/>
+      <c r="C28" s="146"/>
+      <c r="D28" s="147" t="s">
         <v>78</v>
       </c>
-      <c r="E28" s="140"/>
-      <c r="F28" s="140"/>
-      <c r="G28" s="140" t="s">
+      <c r="E28" s="146"/>
+      <c r="F28" s="146"/>
+      <c r="G28" s="146" t="s">
         <v>79</v>
       </c>
-      <c r="H28" s="140"/>
-      <c r="I28" s="140"/>
-      <c r="J28" s="141" t="s">
+      <c r="H28" s="146"/>
+      <c r="I28" s="146"/>
+      <c r="J28" s="147" t="s">
         <v>80</v>
       </c>
-      <c r="K28" s="116"/>
-      <c r="L28" s="116"/>
-      <c r="M28" s="140"/>
-      <c r="N28" s="140"/>
-      <c r="O28" s="141" t="s">
+      <c r="K28" s="122"/>
+      <c r="L28" s="122"/>
+      <c r="M28" s="146"/>
+      <c r="N28" s="146"/>
+      <c r="O28" s="147" t="s">
         <v>81</v>
       </c>
-      <c r="P28" s="116"/>
-      <c r="Q28" s="142"/>
+      <c r="P28" s="122"/>
+      <c r="Q28" s="148"/>
     </row>
     <row r="29" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A29" s="79" t="s">
+      <c r="A29" s="85" t="s">
         <v>82</v>
       </c>
-      <c r="B29" s="80"/>
-      <c r="C29" s="80"/>
-      <c r="D29" s="80"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="80"/>
-      <c r="G29" s="106" t="s">
+      <c r="B29" s="86"/>
+      <c r="C29" s="86"/>
+      <c r="D29" s="86"/>
+      <c r="E29" s="86"/>
+      <c r="F29" s="86"/>
+      <c r="G29" s="112" t="s">
         <v>83</v>
       </c>
-      <c r="H29" s="80"/>
-      <c r="I29" s="80"/>
-      <c r="J29" s="80"/>
-      <c r="K29" s="80"/>
-      <c r="L29" s="82"/>
-      <c r="M29" s="85" t="s">
+      <c r="H29" s="86"/>
+      <c r="I29" s="86"/>
+      <c r="J29" s="86"/>
+      <c r="K29" s="86"/>
+      <c r="L29" s="88"/>
+      <c r="M29" s="91" t="s">
         <v>84</v>
       </c>
-      <c r="N29" s="80"/>
-      <c r="O29" s="80"/>
-      <c r="P29" s="80"/>
-      <c r="Q29" s="82"/>
+      <c r="N29" s="86"/>
+      <c r="O29" s="86"/>
+      <c r="P29" s="86"/>
+      <c r="Q29" s="88"/>
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A30" s="86"/>
-      <c r="B30" s="87"/>
-      <c r="C30" s="87"/>
-      <c r="D30" s="87"/>
-      <c r="E30" s="87"/>
-      <c r="F30" s="87"/>
-      <c r="G30" s="87"/>
-      <c r="H30" s="87"/>
-      <c r="I30" s="87"/>
-      <c r="J30" s="87"/>
-      <c r="K30" s="87"/>
-      <c r="L30" s="87"/>
-      <c r="M30" s="96"/>
-      <c r="Q30" s="143"/>
+      <c r="A30" s="92"/>
+      <c r="B30" s="93"/>
+      <c r="C30" s="93"/>
+      <c r="D30" s="93"/>
+      <c r="E30" s="93"/>
+      <c r="F30" s="93"/>
+      <c r="G30" s="93"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="93"/>
+      <c r="J30" s="93"/>
+      <c r="K30" s="93"/>
+      <c r="L30" s="93"/>
+      <c r="M30" s="102"/>
+      <c r="Q30" s="149"/>
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A31" s="144" t="s">
+      <c r="A31" s="150" t="s">
         <v>85</v>
       </c>
-      <c r="B31" s="78"/>
-      <c r="C31" s="145"/>
-      <c r="D31" s="78"/>
-      <c r="E31" s="78"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="78"/>
-      <c r="H31" s="146"/>
-      <c r="I31" s="146"/>
-      <c r="J31" s="145" t="s">
+      <c r="B31" s="84"/>
+      <c r="C31" s="151"/>
+      <c r="D31" s="84"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="152"/>
+      <c r="I31" s="152"/>
+      <c r="J31" s="151" t="s">
         <v>86</v>
       </c>
-      <c r="K31" s="78"/>
-      <c r="L31" s="146"/>
-      <c r="M31" s="102"/>
-      <c r="N31" s="78"/>
-      <c r="O31" s="78"/>
-      <c r="P31" s="78"/>
-      <c r="Q31" s="97"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="152"/>
+      <c r="M31" s="108"/>
+      <c r="N31" s="84"/>
+      <c r="O31" s="84"/>
+      <c r="P31" s="84"/>
+      <c r="Q31" s="103"/>
     </row>
     <row r="32" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A32" s="147" t="s">
+      <c r="A32" s="153" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="80"/>
-      <c r="C32" s="80"/>
-      <c r="D32" s="80"/>
-      <c r="E32" s="80"/>
-      <c r="F32" s="80"/>
-      <c r="G32" s="80"/>
-      <c r="H32" s="80"/>
-      <c r="I32" s="80"/>
-      <c r="J32" s="80"/>
-      <c r="K32" s="80"/>
-      <c r="L32" s="80"/>
-      <c r="M32" s="80"/>
-      <c r="N32" s="80"/>
-      <c r="O32" s="80"/>
-      <c r="P32" s="80"/>
-      <c r="Q32" s="80"/>
+      <c r="B32" s="86"/>
+      <c r="C32" s="86"/>
+      <c r="D32" s="86"/>
+      <c r="E32" s="86"/>
+      <c r="F32" s="86"/>
+      <c r="G32" s="86"/>
+      <c r="H32" s="86"/>
+      <c r="I32" s="86"/>
+      <c r="J32" s="86"/>
+      <c r="K32" s="86"/>
+      <c r="L32" s="86"/>
+      <c r="M32" s="86"/>
+      <c r="N32" s="86"/>
+      <c r="O32" s="86"/>
+      <c r="P32" s="86"/>
+      <c r="Q32" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="99">
@@ -3576,60 +3592,120 @@
       <c r="A20" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="G20" s="8"/>
+      <c r="B20" s="70"/>
+      <c r="C20" s="70"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="71"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="7"/>
-      <c r="G21" s="8"/>
+      <c r="A21" s="72"/>
+      <c r="B21" s="70"/>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="71"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="7"/>
-      <c r="G22" s="8"/>
+      <c r="A22" s="72"/>
+      <c r="B22" s="70"/>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="71"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="7"/>
-      <c r="G23" s="8"/>
+      <c r="A23" s="72"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="71"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="7"/>
-      <c r="G24" s="8"/>
+      <c r="A24" s="72"/>
+      <c r="B24" s="70"/>
+      <c r="C24" s="70"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="71"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="7"/>
-      <c r="G25" s="8"/>
+      <c r="A25" s="72"/>
+      <c r="B25" s="70"/>
+      <c r="C25" s="70"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="71"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="7"/>
-      <c r="G26" s="8"/>
+      <c r="A26" s="72"/>
+      <c r="B26" s="70"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="71"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="7"/>
-      <c r="G27" s="8"/>
+      <c r="A27" s="72"/>
+      <c r="B27" s="70"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="71"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="7"/>
-      <c r="G28" s="8"/>
+      <c r="A28" s="72"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="71"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="7"/>
-      <c r="G29" s="8"/>
+      <c r="A29" s="72"/>
+      <c r="B29" s="70"/>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="71"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="7"/>
-      <c r="G30" s="8"/>
+      <c r="A30" s="72"/>
+      <c r="B30" s="70"/>
+      <c r="C30" s="70"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="71"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="7"/>
-      <c r="G31" s="8"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="10"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="12"/>
+      <c r="A31" s="72"/>
+      <c r="B31" s="70"/>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="71"/>
+    </row>
+    <row r="32" ht="64" customHeight="1" spans="1:7">
+      <c r="A32" s="73"/>
+      <c r="B32" s="74"/>
+      <c r="C32" s="74"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="74"/>
+      <c r="F32" s="74"/>
+      <c r="G32" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/backend/src/main/resources/templates/alltemple_template-lead.xlsx
+++ b/backend/src/main/resources/templates/alltemple_template-lead.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\lead-declaration-system\backend\src\main\resources\templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="1"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="报关单" sheetId="1" r:id="rId1"/>
@@ -376,6 +381,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>ACCOUNT NAME</t>
     </r>
     <r>
@@ -516,9 +527,9 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="178" formatCode="#,##0.0000_);[Red]\(#,##0.0000\)"/>
-    <numFmt numFmtId="179" formatCode="0.0000_ "/>
+    <numFmt numFmtId="177" formatCode="0.0000_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="179" formatCode="#,##0.0000_);[Red]\(#,##0.0000\)"/>
   </numFmts>
   <fonts count="38">
     <font>
@@ -1543,7 +1554,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1614,6 +1625,9 @@
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1654,6 +1668,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1889,12 +1906,12 @@
     <xf numFmtId="49" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1913,22 +1930,22 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1937,10 +1954,10 @@
     <xf numFmtId="49" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2454,800 +2471,800 @@
   <dimension ref="A1:T32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.3796296296296" style="80" customWidth="1"/>
-    <col min="2" max="2" width="8.87962962962963" style="80" customWidth="1"/>
-    <col min="3" max="3" width="11.1111111111111" style="80" customWidth="1"/>
-    <col min="4" max="4" width="4.44444444444444" style="80" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6296296296296" style="80" customWidth="1"/>
-    <col min="6" max="6" width="13" style="80" customWidth="1"/>
-    <col min="7" max="7" width="9.77777777777778" style="80" customWidth="1"/>
-    <col min="8" max="8" width="11.6296296296296" style="80" customWidth="1"/>
-    <col min="9" max="9" width="10" style="80" customWidth="1"/>
-    <col min="10" max="10" width="4.62962962962963" style="80" customWidth="1"/>
-    <col min="11" max="11" width="16.3333333333333" style="80" customWidth="1"/>
-    <col min="12" max="12" width="6.5" style="80" customWidth="1"/>
-    <col min="13" max="13" width="8.77777777777778" style="80" customWidth="1"/>
-    <col min="14" max="14" width="3.87962962962963" style="80" customWidth="1"/>
-    <col min="15" max="15" width="6.75" style="80" customWidth="1"/>
-    <col min="16" max="16" width="6.66666666666667" style="80" customWidth="1"/>
-    <col min="17" max="17" width="18.6666666666667" style="80" customWidth="1"/>
-    <col min="18" max="19" width="9" style="80" customWidth="1"/>
-    <col min="20" max="20" width="12.75" style="80" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="80" customWidth="1"/>
+    <col min="1" max="1" width="14.3796296296296" style="82" customWidth="1"/>
+    <col min="2" max="2" width="8.87962962962963" style="82" customWidth="1"/>
+    <col min="3" max="3" width="11.1111111111111" style="82" customWidth="1"/>
+    <col min="4" max="4" width="4.44444444444444" style="82" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6296296296296" style="82" customWidth="1"/>
+    <col min="6" max="6" width="13" style="82" customWidth="1"/>
+    <col min="7" max="7" width="9.77777777777778" style="82" customWidth="1"/>
+    <col min="8" max="8" width="11.6296296296296" style="82" customWidth="1"/>
+    <col min="9" max="9" width="10" style="82" customWidth="1"/>
+    <col min="10" max="10" width="4.62962962962963" style="82" customWidth="1"/>
+    <col min="11" max="11" width="16.3333333333333" style="82" customWidth="1"/>
+    <col min="12" max="12" width="6.5" style="82" customWidth="1"/>
+    <col min="13" max="13" width="8.77777777777778" style="82" customWidth="1"/>
+    <col min="14" max="14" width="3.87962962962963" style="82" customWidth="1"/>
+    <col min="15" max="15" width="6.75" style="82" customWidth="1"/>
+    <col min="16" max="16" width="6.66666666666667" style="82" customWidth="1"/>
+    <col min="17" max="17" width="18.6666666666667" style="82" customWidth="1"/>
+    <col min="18" max="19" width="9" style="82" customWidth="1"/>
+    <col min="20" max="20" width="12.75" style="82" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="82" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="53.25" customHeight="1" spans="1:20">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="S1" s="80" t="s">
+      <c r="S1" s="82" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" s="76" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A2" s="82" t="s">
+    <row r="2" s="78" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A2" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="76" t="s">
+      <c r="C2" s="85"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="83"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="84"/>
-      <c r="P2" s="84"/>
-      <c r="Q2" s="84"/>
-    </row>
-    <row r="3" s="77" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A3" s="85" t="s">
+      <c r="F2" s="85"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="86"/>
+      <c r="O2" s="86"/>
+      <c r="P2" s="86"/>
+      <c r="Q2" s="86"/>
+    </row>
+    <row r="3" s="79" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A3" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="87" t="s">
+      <c r="B3" s="88"/>
+      <c r="C3" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="88"/>
-      <c r="E3" s="89" t="s">
+      <c r="D3" s="90"/>
+      <c r="E3" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="90"/>
-      <c r="G3" s="91" t="s">
+      <c r="F3" s="92"/>
+      <c r="G3" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="85" t="s">
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
-      <c r="N3" s="91" t="s">
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="88"/>
-    </row>
-    <row r="4" s="77" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A4" s="92" t="s">
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="90"/>
+    </row>
+    <row r="4" s="79" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A4" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="93"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="92" t="s">
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="98"/>
-      <c r="K4" s="92" t="s">
+      <c r="H4" s="95"/>
+      <c r="I4" s="95"/>
+      <c r="J4" s="100"/>
+      <c r="K4" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="93"/>
-      <c r="M4" s="93"/>
-      <c r="N4" s="92" t="s">
+      <c r="L4" s="95"/>
+      <c r="M4" s="95"/>
+      <c r="N4" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="93"/>
-      <c r="P4" s="93"/>
-      <c r="Q4" s="98"/>
+      <c r="O4" s="95"/>
+      <c r="P4" s="95"/>
+      <c r="Q4" s="100"/>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:20">
-      <c r="A5" s="99" t="s">
+      <c r="A5" s="101" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="99"/>
-      <c r="L5" s="84"/>
-      <c r="M5" s="84"/>
-      <c r="N5" s="102"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="103"/>
-    </row>
-    <row r="6" s="77" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A6" s="85" t="s">
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="86"/>
+      <c r="I5" s="86"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="101"/>
+      <c r="L5" s="86"/>
+      <c r="M5" s="86"/>
+      <c r="N5" s="104"/>
+      <c r="O5" s="86"/>
+      <c r="P5" s="86"/>
+      <c r="Q5" s="105"/>
+    </row>
+    <row r="6" s="79" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A6" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="86"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="89" t="s">
+      <c r="B6" s="88"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="90"/>
-      <c r="G6" s="91" t="s">
+      <c r="F6" s="92"/>
+      <c r="G6" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="104" t="s">
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="90"/>
+      <c r="K6" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="86"/>
-      <c r="M6" s="86"/>
-      <c r="N6" s="86"/>
-      <c r="O6" s="86"/>
-      <c r="P6" s="86"/>
-      <c r="Q6" s="88"/>
+      <c r="L6" s="88"/>
+      <c r="M6" s="88"/>
+      <c r="N6" s="88"/>
+      <c r="O6" s="88"/>
+      <c r="P6" s="88"/>
+      <c r="Q6" s="90"/>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:20">
-      <c r="A7" s="105" t="s">
+      <c r="A7" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="106"/>
-      <c r="C7" s="106"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="102" t="s">
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="109"/>
+      <c r="E7" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="103"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="84"/>
-      <c r="J7" s="103"/>
-      <c r="K7" s="108"/>
-      <c r="L7" s="84"/>
-      <c r="M7" s="84"/>
-      <c r="N7" s="84"/>
-      <c r="O7" s="84"/>
-      <c r="P7" s="84"/>
-      <c r="Q7" s="103"/>
-    </row>
-    <row r="8" s="77" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A8" s="85" t="s">
+      <c r="F7" s="105"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="86"/>
+      <c r="J7" s="105"/>
+      <c r="K7" s="110"/>
+      <c r="L7" s="86"/>
+      <c r="M7" s="86"/>
+      <c r="N7" s="86"/>
+      <c r="O7" s="86"/>
+      <c r="P7" s="86"/>
+      <c r="Q7" s="105"/>
+    </row>
+    <row r="8" s="79" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A8" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="86"/>
-      <c r="C8" s="87"/>
-      <c r="D8" s="88"/>
-      <c r="E8" s="89" t="s">
+      <c r="B8" s="88"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="90"/>
+      <c r="E8" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="109"/>
-      <c r="G8" s="85" t="s">
+      <c r="F8" s="111"/>
+      <c r="G8" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="86"/>
-      <c r="I8" s="109"/>
-      <c r="J8" s="88"/>
-      <c r="K8" s="104" t="s">
+      <c r="H8" s="88"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="106" t="s">
         <v>23</v>
       </c>
-      <c r="L8" s="86"/>
-      <c r="M8" s="86"/>
-      <c r="N8" s="86"/>
-      <c r="O8" s="86"/>
-      <c r="P8" s="86"/>
-      <c r="Q8" s="88"/>
-      <c r="T8" s="80"/>
+      <c r="L8" s="88"/>
+      <c r="M8" s="88"/>
+      <c r="N8" s="88"/>
+      <c r="O8" s="88"/>
+      <c r="P8" s="88"/>
+      <c r="Q8" s="90"/>
+      <c r="T8" s="82"/>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:20">
-      <c r="A9" s="102" t="s">
+      <c r="A9" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="84"/>
-      <c r="C9" s="84"/>
-      <c r="D9" s="103"/>
-      <c r="E9" s="110" t="s">
+      <c r="B9" s="86"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="103"/>
-      <c r="G9" s="110" t="s">
+      <c r="F9" s="105"/>
+      <c r="G9" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="84"/>
-      <c r="I9" s="84"/>
-      <c r="J9" s="103"/>
-      <c r="K9" s="108"/>
-      <c r="L9" s="84"/>
-      <c r="M9" s="84"/>
-      <c r="N9" s="84"/>
-      <c r="O9" s="84"/>
-      <c r="P9" s="84"/>
-      <c r="Q9" s="103"/>
-    </row>
-    <row r="10" s="77" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A10" s="85" t="s">
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="110"/>
+      <c r="L9" s="86"/>
+      <c r="M9" s="86"/>
+      <c r="N9" s="86"/>
+      <c r="O9" s="86"/>
+      <c r="P9" s="86"/>
+      <c r="Q9" s="105"/>
+    </row>
+    <row r="10" s="79" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A10" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="86"/>
-      <c r="C10" s="87"/>
-      <c r="D10" s="88"/>
-      <c r="E10" s="89" t="s">
+      <c r="B10" s="88"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="90"/>
-      <c r="G10" s="85" t="s">
+      <c r="F10" s="92"/>
+      <c r="G10" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="86"/>
-      <c r="I10" s="87"/>
-      <c r="J10" s="88"/>
-      <c r="K10" s="85" t="s">
+      <c r="H10" s="88"/>
+      <c r="I10" s="89"/>
+      <c r="J10" s="90"/>
+      <c r="K10" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="87" t="s">
+      <c r="L10" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="M10" s="88"/>
-      <c r="N10" s="85" t="s">
+      <c r="M10" s="90"/>
+      <c r="N10" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="O10" s="86"/>
-      <c r="P10" s="87" t="s">
+      <c r="O10" s="88"/>
+      <c r="P10" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="Q10" s="88"/>
-      <c r="T10" s="80"/>
+      <c r="Q10" s="90"/>
+      <c r="T10" s="82"/>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:20">
-      <c r="A11" s="102" t="s">
+      <c r="A11" s="104" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="84"/>
-      <c r="C11" s="84"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="102" t="s">
+      <c r="B11" s="86"/>
+      <c r="C11" s="86"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="104" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="107"/>
-      <c r="G11" s="102" t="s">
+      <c r="F11" s="109"/>
+      <c r="G11" s="104" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="106"/>
-      <c r="I11" s="106"/>
-      <c r="J11" s="107"/>
-      <c r="K11" s="102" t="s">
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="109"/>
+      <c r="K11" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="L11" s="84"/>
-      <c r="M11" s="103"/>
-      <c r="N11" s="102" t="s">
+      <c r="L11" s="86"/>
+      <c r="M11" s="105"/>
+      <c r="N11" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="O11" s="84"/>
-      <c r="P11" s="84"/>
-      <c r="Q11" s="103"/>
-    </row>
-    <row r="12" s="77" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A12" s="85" t="s">
+      <c r="O11" s="86"/>
+      <c r="P11" s="86"/>
+      <c r="Q11" s="105"/>
+    </row>
+    <row r="12" s="79" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A12" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="86"/>
-      <c r="C12" s="87"/>
-      <c r="D12" s="88"/>
-      <c r="E12" s="111" t="s">
+      <c r="B12" s="88"/>
+      <c r="C12" s="89"/>
+      <c r="D12" s="90"/>
+      <c r="E12" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="111" t="s">
+      <c r="F12" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="91" t="s">
+      <c r="G12" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="H12" s="88"/>
-      <c r="I12" s="85" t="s">
+      <c r="H12" s="90"/>
+      <c r="I12" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="J12" s="112"/>
-      <c r="K12" s="85" t="s">
+      <c r="J12" s="114"/>
+      <c r="K12" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="L12" s="86"/>
-      <c r="M12" s="91" t="s">
+      <c r="L12" s="88"/>
+      <c r="M12" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="N12" s="86"/>
-      <c r="O12" s="88"/>
-      <c r="P12" s="91" t="s">
+      <c r="N12" s="88"/>
+      <c r="O12" s="90"/>
+      <c r="P12" s="93" t="s">
         <v>42</v>
       </c>
-      <c r="Q12" s="88"/>
-      <c r="T12" s="80"/>
+      <c r="Q12" s="90"/>
+      <c r="T12" s="82"/>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:20">
-      <c r="A13" s="102" t="s">
+      <c r="A13" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="84"/>
-      <c r="C13" s="84"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="102" t="s">
+      <c r="B13" s="86"/>
+      <c r="C13" s="86"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="104" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="102" t="s">
+      <c r="F13" s="104" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="102" t="s">
+      <c r="G13" s="104" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="103"/>
-      <c r="I13" s="113" t="s">
+      <c r="H13" s="105"/>
+      <c r="I13" s="115" t="s">
         <v>47</v>
       </c>
-      <c r="J13" s="101"/>
-      <c r="K13" s="114" t="s">
+      <c r="J13" s="103"/>
+      <c r="K13" s="116" t="s">
         <v>48</v>
       </c>
-      <c r="L13" s="84"/>
-      <c r="M13" s="102" t="s">
+      <c r="L13" s="86"/>
+      <c r="M13" s="104" t="s">
         <v>49</v>
       </c>
-      <c r="N13" s="84"/>
-      <c r="O13" s="103"/>
-      <c r="P13" s="102" t="s">
+      <c r="N13" s="86"/>
+      <c r="O13" s="105"/>
+      <c r="P13" s="104" t="s">
         <v>50</v>
       </c>
-      <c r="Q13" s="103"/>
-    </row>
-    <row r="14" s="77" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A14" s="91" t="s">
+      <c r="Q13" s="105"/>
+    </row>
+    <row r="14" s="79" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A14" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="86"/>
-      <c r="C14" s="86"/>
-      <c r="D14" s="86"/>
-      <c r="E14" s="86"/>
-      <c r="F14" s="86"/>
-      <c r="G14" s="86"/>
-      <c r="H14" s="86"/>
-      <c r="I14" s="86"/>
-      <c r="J14" s="86"/>
-      <c r="K14" s="86"/>
-      <c r="L14" s="86"/>
-      <c r="M14" s="86"/>
-      <c r="N14" s="86"/>
-      <c r="O14" s="86"/>
-      <c r="P14" s="86"/>
-      <c r="Q14" s="88"/>
-      <c r="T14" s="80"/>
-    </row>
-    <row r="15" s="78" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A15" s="115" t="s">
+      <c r="B14" s="88"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="88"/>
+      <c r="E14" s="88"/>
+      <c r="F14" s="88"/>
+      <c r="G14" s="88"/>
+      <c r="H14" s="88"/>
+      <c r="I14" s="88"/>
+      <c r="J14" s="88"/>
+      <c r="K14" s="88"/>
+      <c r="L14" s="88"/>
+      <c r="M14" s="88"/>
+      <c r="N14" s="88"/>
+      <c r="O14" s="88"/>
+      <c r="P14" s="88"/>
+      <c r="Q14" s="90"/>
+      <c r="T14" s="82"/>
+    </row>
+    <row r="15" s="80" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A15" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="84"/>
-      <c r="C15" s="84"/>
-      <c r="D15" s="84"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="84"/>
-      <c r="G15" s="84"/>
-      <c r="H15" s="116" t="s">
+      <c r="B15" s="86"/>
+      <c r="C15" s="86"/>
+      <c r="D15" s="86"/>
+      <c r="E15" s="86"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="I15" s="84"/>
-      <c r="J15" s="84"/>
-      <c r="K15" s="84"/>
-      <c r="L15" s="84"/>
-      <c r="M15" s="84"/>
-      <c r="N15" s="84"/>
-      <c r="O15" s="84"/>
-      <c r="P15" s="84"/>
-      <c r="Q15" s="103"/>
-      <c r="T15" s="80"/>
-    </row>
-    <row r="16" s="77" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A16" s="89" t="s">
+      <c r="I15" s="86"/>
+      <c r="J15" s="86"/>
+      <c r="K15" s="86"/>
+      <c r="L15" s="86"/>
+      <c r="M15" s="86"/>
+      <c r="N15" s="86"/>
+      <c r="O15" s="86"/>
+      <c r="P15" s="86"/>
+      <c r="Q15" s="105"/>
+      <c r="T15" s="82"/>
+    </row>
+    <row r="16" s="79" customFormat="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A16" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="117"/>
-      <c r="C16" s="118"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="117"/>
-      <c r="I16" s="117"/>
-      <c r="J16" s="117"/>
-      <c r="K16" s="117"/>
-      <c r="L16" s="117"/>
-      <c r="M16" s="117"/>
-      <c r="N16" s="117"/>
-      <c r="O16" s="117"/>
-      <c r="P16" s="117"/>
-      <c r="Q16" s="119"/>
-      <c r="T16" s="80"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="120"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="119"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="119"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="119"/>
+      <c r="K16" s="119"/>
+      <c r="L16" s="119"/>
+      <c r="M16" s="119"/>
+      <c r="N16" s="119"/>
+      <c r="O16" s="119"/>
+      <c r="P16" s="119"/>
+      <c r="Q16" s="121"/>
+      <c r="T16" s="82"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A17" s="102" t="s">
+      <c r="A17" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="84"/>
-      <c r="C17" s="84"/>
-      <c r="D17" s="84"/>
-      <c r="E17" s="84"/>
-      <c r="F17" s="84"/>
-      <c r="G17" s="84"/>
-      <c r="H17" s="84"/>
-      <c r="I17" s="84"/>
-      <c r="J17" s="84"/>
-      <c r="K17" s="84"/>
-      <c r="L17" s="84"/>
-      <c r="M17" s="84"/>
-      <c r="N17" s="84"/>
-      <c r="O17" s="84"/>
-      <c r="P17" s="84"/>
-      <c r="Q17" s="103"/>
-    </row>
-    <row r="18" s="79" customFormat="1" ht="18.75" customHeight="1" spans="1:20">
-      <c r="A18" s="120" t="s">
+      <c r="B17" s="86"/>
+      <c r="C17" s="86"/>
+      <c r="D17" s="86"/>
+      <c r="E17" s="86"/>
+      <c r="F17" s="86"/>
+      <c r="G17" s="86"/>
+      <c r="H17" s="86"/>
+      <c r="I17" s="86"/>
+      <c r="J17" s="86"/>
+      <c r="K17" s="86"/>
+      <c r="L17" s="86"/>
+      <c r="M17" s="86"/>
+      <c r="N17" s="86"/>
+      <c r="O17" s="86"/>
+      <c r="P17" s="86"/>
+      <c r="Q17" s="105"/>
+    </row>
+    <row r="18" s="81" customFormat="1" ht="18.75" customHeight="1" spans="1:20">
+      <c r="A18" s="122" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="121" t="s">
+      <c r="B18" s="123" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="122"/>
-      <c r="D18" s="121" t="s">
+      <c r="C18" s="124"/>
+      <c r="D18" s="123" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="121" t="s">
+      <c r="E18" s="124"/>
+      <c r="F18" s="124"/>
+      <c r="G18" s="123" t="s">
         <v>59</v>
       </c>
-      <c r="H18" s="121" t="s">
+      <c r="H18" s="123" t="s">
         <v>60</v>
       </c>
-      <c r="I18" s="122"/>
-      <c r="J18" s="122"/>
-      <c r="K18" s="121" t="s">
+      <c r="I18" s="124"/>
+      <c r="J18" s="124"/>
+      <c r="K18" s="123" t="s">
         <v>61</v>
       </c>
-      <c r="L18" s="121" t="s">
+      <c r="L18" s="123" t="s">
         <v>62</v>
       </c>
-      <c r="M18" s="122"/>
-      <c r="N18" s="121" t="s">
+      <c r="M18" s="124"/>
+      <c r="N18" s="123" t="s">
         <v>63</v>
       </c>
-      <c r="O18" s="122"/>
-      <c r="P18" s="122"/>
-      <c r="Q18" s="123" t="s">
+      <c r="O18" s="124"/>
+      <c r="P18" s="124"/>
+      <c r="Q18" s="125" t="s">
         <v>64</v>
       </c>
-      <c r="T18" s="80"/>
-    </row>
-    <row r="19" s="80" customFormat="1" spans="1:20">
-      <c r="A19" s="124" t="s">
+      <c r="T18" s="82"/>
+    </row>
+    <row r="19" s="82" customFormat="1" spans="1:20">
+      <c r="A19" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="125" t="s">
+      <c r="B19" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="86"/>
-      <c r="D19" s="125" t="s">
+      <c r="C19" s="88"/>
+      <c r="D19" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="86"/>
-      <c r="F19" s="86"/>
-      <c r="G19" s="125" t="s">
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="127" t="s">
         <v>68</v>
       </c>
-      <c r="H19" s="126" t="s">
+      <c r="H19" s="128" t="s">
         <v>69</v>
       </c>
-      <c r="I19" s="127" t="s">
+      <c r="I19" s="129" t="s">
         <v>70</v>
       </c>
-      <c r="J19" s="128" t="s">
+      <c r="J19" s="130" t="s">
         <v>71</v>
       </c>
-      <c r="K19" s="129" t="s">
+      <c r="K19" s="131" t="s">
         <v>72</v>
       </c>
-      <c r="L19" s="125" t="s">
+      <c r="L19" s="127" t="s">
         <v>73</v>
       </c>
-      <c r="M19" s="86"/>
-      <c r="N19" s="125" t="s">
+      <c r="M19" s="88"/>
+      <c r="N19" s="127" t="s">
         <v>74</v>
       </c>
-      <c r="O19" s="86"/>
-      <c r="P19" s="86"/>
-      <c r="Q19" s="130" t="s">
+      <c r="O19" s="88"/>
+      <c r="P19" s="88"/>
+      <c r="Q19" s="132" t="s">
         <v>75</v>
       </c>
-      <c r="R19" s="131"/>
-    </row>
-    <row r="20" s="80" customFormat="1" spans="1:20">
-      <c r="A20" s="132"/>
-      <c r="B20" s="133"/>
-      <c r="C20" s="133"/>
-      <c r="D20" s="134" t="s">
+      <c r="R19" s="133"/>
+    </row>
+    <row r="20" s="82" customFormat="1" spans="1:20">
+      <c r="A20" s="134"/>
+      <c r="B20" s="135"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="136" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="134"/>
-      <c r="F20" s="134"/>
-      <c r="G20" s="135" t="s">
+      <c r="E20" s="136"/>
+      <c r="F20" s="136"/>
+      <c r="G20" s="137" t="s">
         <v>77</v>
       </c>
-      <c r="H20" s="136"/>
-      <c r="I20" s="136"/>
-      <c r="J20" s="137"/>
-      <c r="K20" s="138"/>
-      <c r="L20" s="133"/>
-      <c r="M20" s="133"/>
-      <c r="N20" s="133"/>
-      <c r="O20" s="133"/>
-      <c r="P20" s="133"/>
-      <c r="Q20" s="139"/>
-      <c r="R20" s="131"/>
-    </row>
-    <row r="21" s="80" customFormat="1" ht="39" customHeight="1" spans="1:20">
-      <c r="A21" s="132"/>
-      <c r="B21" s="133"/>
-      <c r="D21" s="134"/>
-      <c r="E21" s="134"/>
-      <c r="F21" s="134"/>
-      <c r="G21" s="135"/>
-      <c r="H21" s="140"/>
-      <c r="K21" s="141"/>
-      <c r="L21" s="133"/>
-      <c r="N21" s="133"/>
-      <c r="Q21" s="139"/>
-      <c r="R21" s="131"/>
-    </row>
-    <row r="22" s="80" customFormat="1" spans="1:20">
-      <c r="A22" s="124"/>
-      <c r="B22" s="125"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="125"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="86"/>
-      <c r="G22" s="125"/>
-      <c r="H22" s="142"/>
-      <c r="I22" s="143"/>
-      <c r="J22" s="144"/>
-      <c r="K22" s="129"/>
-      <c r="L22" s="125"/>
-      <c r="M22" s="86"/>
-      <c r="N22" s="125"/>
-      <c r="O22" s="86"/>
-      <c r="P22" s="86"/>
-      <c r="Q22" s="130"/>
-      <c r="R22" s="131"/>
-    </row>
-    <row r="23" s="80" customFormat="1" spans="1:20">
-      <c r="A23" s="132"/>
-      <c r="B23" s="133"/>
-      <c r="C23" s="133"/>
-      <c r="D23" s="134"/>
-      <c r="E23" s="134"/>
-      <c r="F23" s="134"/>
-      <c r="G23" s="135"/>
-      <c r="H23" s="136"/>
-      <c r="I23" s="136"/>
-      <c r="J23" s="137"/>
-      <c r="K23" s="138"/>
-      <c r="L23" s="133"/>
-      <c r="M23" s="133"/>
-      <c r="N23" s="133"/>
-      <c r="O23" s="133"/>
-      <c r="P23" s="133"/>
-      <c r="Q23" s="139"/>
-      <c r="R23" s="131"/>
-    </row>
-    <row r="24" s="80" customFormat="1" ht="40" customHeight="1" spans="1:20">
-      <c r="A24" s="132"/>
-      <c r="B24" s="133"/>
-      <c r="D24" s="134"/>
-      <c r="E24" s="134"/>
-      <c r="F24" s="134"/>
-      <c r="G24" s="135"/>
-      <c r="H24" s="140"/>
-      <c r="K24" s="141"/>
-      <c r="L24" s="133"/>
-      <c r="N24" s="133"/>
-      <c r="Q24" s="139"/>
-      <c r="R24" s="131"/>
-    </row>
-    <row r="25" s="80" customFormat="1" spans="1:20">
-      <c r="A25" s="124"/>
-      <c r="B25" s="125"/>
-      <c r="C25" s="86"/>
-      <c r="D25" s="125"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="125"/>
-      <c r="H25" s="143"/>
-      <c r="I25" s="143"/>
-      <c r="J25" s="144"/>
-      <c r="K25" s="129"/>
-      <c r="L25" s="125"/>
-      <c r="M25" s="86"/>
-      <c r="N25" s="125"/>
-      <c r="O25" s="86"/>
-      <c r="P25" s="86"/>
-      <c r="Q25" s="130"/>
-      <c r="R25" s="131"/>
-    </row>
-    <row r="26" s="80" customFormat="1" spans="1:20">
-      <c r="A26" s="132"/>
-      <c r="B26" s="133"/>
-      <c r="C26" s="133"/>
-      <c r="D26" s="134"/>
-      <c r="E26" s="134"/>
-      <c r="F26" s="134"/>
-      <c r="G26" s="135"/>
-      <c r="H26" s="136"/>
-      <c r="I26" s="136"/>
-      <c r="J26" s="137"/>
-      <c r="K26" s="138"/>
-      <c r="L26" s="133"/>
-      <c r="M26" s="133"/>
-      <c r="N26" s="133"/>
-      <c r="O26" s="133"/>
-      <c r="P26" s="133"/>
-      <c r="Q26" s="139"/>
-      <c r="R26" s="131"/>
-    </row>
-    <row r="27" s="80" customFormat="1" ht="42" customHeight="1" spans="1:20">
-      <c r="A27" s="132"/>
-      <c r="B27" s="133"/>
-      <c r="D27" s="134"/>
-      <c r="E27" s="134"/>
-      <c r="F27" s="134"/>
-      <c r="G27" s="135"/>
-      <c r="H27" s="140"/>
-      <c r="K27" s="141"/>
-      <c r="L27" s="133"/>
-      <c r="N27" s="133"/>
-      <c r="Q27" s="139"/>
-      <c r="R27" s="131"/>
-    </row>
-    <row r="28" s="77" customFormat="1" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A28" s="145"/>
-      <c r="B28" s="146"/>
-      <c r="C28" s="146"/>
-      <c r="D28" s="147" t="s">
+      <c r="H20" s="138"/>
+      <c r="I20" s="138"/>
+      <c r="J20" s="139"/>
+      <c r="K20" s="140"/>
+      <c r="L20" s="135"/>
+      <c r="M20" s="135"/>
+      <c r="N20" s="135"/>
+      <c r="O20" s="135"/>
+      <c r="P20" s="135"/>
+      <c r="Q20" s="141"/>
+      <c r="R20" s="133"/>
+    </row>
+    <row r="21" s="82" customFormat="1" ht="39" customHeight="1" spans="1:20">
+      <c r="A21" s="134"/>
+      <c r="B21" s="135"/>
+      <c r="D21" s="136"/>
+      <c r="E21" s="136"/>
+      <c r="F21" s="136"/>
+      <c r="G21" s="137"/>
+      <c r="H21" s="142"/>
+      <c r="K21" s="143"/>
+      <c r="L21" s="135"/>
+      <c r="N21" s="135"/>
+      <c r="Q21" s="141"/>
+      <c r="R21" s="133"/>
+    </row>
+    <row r="22" s="82" customFormat="1" spans="1:20">
+      <c r="A22" s="126"/>
+      <c r="B22" s="127"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="127"/>
+      <c r="E22" s="88"/>
+      <c r="F22" s="88"/>
+      <c r="G22" s="127"/>
+      <c r="H22" s="144"/>
+      <c r="I22" s="145"/>
+      <c r="J22" s="146"/>
+      <c r="K22" s="131"/>
+      <c r="L22" s="127"/>
+      <c r="M22" s="88"/>
+      <c r="N22" s="127"/>
+      <c r="O22" s="88"/>
+      <c r="P22" s="88"/>
+      <c r="Q22" s="132"/>
+      <c r="R22" s="133"/>
+    </row>
+    <row r="23" s="82" customFormat="1" spans="1:20">
+      <c r="A23" s="134"/>
+      <c r="B23" s="135"/>
+      <c r="C23" s="135"/>
+      <c r="D23" s="136"/>
+      <c r="E23" s="136"/>
+      <c r="F23" s="136"/>
+      <c r="G23" s="137"/>
+      <c r="H23" s="138"/>
+      <c r="I23" s="138"/>
+      <c r="J23" s="139"/>
+      <c r="K23" s="140"/>
+      <c r="L23" s="135"/>
+      <c r="M23" s="135"/>
+      <c r="N23" s="135"/>
+      <c r="O23" s="135"/>
+      <c r="P23" s="135"/>
+      <c r="Q23" s="141"/>
+      <c r="R23" s="133"/>
+    </row>
+    <row r="24" s="82" customFormat="1" ht="40" customHeight="1" spans="1:20">
+      <c r="A24" s="134"/>
+      <c r="B24" s="135"/>
+      <c r="D24" s="136"/>
+      <c r="E24" s="136"/>
+      <c r="F24" s="136"/>
+      <c r="G24" s="137"/>
+      <c r="H24" s="142"/>
+      <c r="K24" s="143"/>
+      <c r="L24" s="135"/>
+      <c r="N24" s="135"/>
+      <c r="Q24" s="141"/>
+      <c r="R24" s="133"/>
+    </row>
+    <row r="25" s="82" customFormat="1" spans="1:20">
+      <c r="A25" s="126"/>
+      <c r="B25" s="127"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="127"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="88"/>
+      <c r="G25" s="127"/>
+      <c r="H25" s="145"/>
+      <c r="I25" s="145"/>
+      <c r="J25" s="146"/>
+      <c r="K25" s="131"/>
+      <c r="L25" s="127"/>
+      <c r="M25" s="88"/>
+      <c r="N25" s="127"/>
+      <c r="O25" s="88"/>
+      <c r="P25" s="88"/>
+      <c r="Q25" s="132"/>
+      <c r="R25" s="133"/>
+    </row>
+    <row r="26" s="82" customFormat="1" spans="1:20">
+      <c r="A26" s="134"/>
+      <c r="B26" s="135"/>
+      <c r="C26" s="135"/>
+      <c r="D26" s="136"/>
+      <c r="E26" s="136"/>
+      <c r="F26" s="136"/>
+      <c r="G26" s="137"/>
+      <c r="H26" s="138"/>
+      <c r="I26" s="138"/>
+      <c r="J26" s="139"/>
+      <c r="K26" s="140"/>
+      <c r="L26" s="135"/>
+      <c r="M26" s="135"/>
+      <c r="N26" s="135"/>
+      <c r="O26" s="135"/>
+      <c r="P26" s="135"/>
+      <c r="Q26" s="141"/>
+      <c r="R26" s="133"/>
+    </row>
+    <row r="27" s="82" customFormat="1" ht="42" customHeight="1" spans="1:20">
+      <c r="A27" s="134"/>
+      <c r="B27" s="135"/>
+      <c r="D27" s="136"/>
+      <c r="E27" s="136"/>
+      <c r="F27" s="136"/>
+      <c r="G27" s="137"/>
+      <c r="H27" s="142"/>
+      <c r="K27" s="143"/>
+      <c r="L27" s="135"/>
+      <c r="N27" s="135"/>
+      <c r="Q27" s="141"/>
+      <c r="R27" s="133"/>
+    </row>
+    <row r="28" s="79" customFormat="1" ht="16.5" customHeight="1" spans="1:20">
+      <c r="A28" s="147"/>
+      <c r="B28" s="148"/>
+      <c r="C28" s="148"/>
+      <c r="D28" s="149" t="s">
         <v>78</v>
       </c>
-      <c r="E28" s="146"/>
-      <c r="F28" s="146"/>
-      <c r="G28" s="146" t="s">
+      <c r="E28" s="148"/>
+      <c r="F28" s="148"/>
+      <c r="G28" s="148" t="s">
         <v>79</v>
       </c>
-      <c r="H28" s="146"/>
-      <c r="I28" s="146"/>
-      <c r="J28" s="147" t="s">
+      <c r="H28" s="148"/>
+      <c r="I28" s="148"/>
+      <c r="J28" s="149" t="s">
         <v>80</v>
       </c>
-      <c r="K28" s="122"/>
-      <c r="L28" s="122"/>
-      <c r="M28" s="146"/>
-      <c r="N28" s="146"/>
-      <c r="O28" s="147" t="s">
+      <c r="K28" s="124"/>
+      <c r="L28" s="124"/>
+      <c r="M28" s="148"/>
+      <c r="N28" s="148"/>
+      <c r="O28" s="149" t="s">
         <v>81</v>
       </c>
-      <c r="P28" s="122"/>
-      <c r="Q28" s="148"/>
+      <c r="P28" s="124"/>
+      <c r="Q28" s="150"/>
     </row>
     <row r="29" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A29" s="85" t="s">
+      <c r="A29" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="B29" s="86"/>
-      <c r="C29" s="86"/>
-      <c r="D29" s="86"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="86"/>
-      <c r="G29" s="112" t="s">
+      <c r="B29" s="88"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="H29" s="86"/>
-      <c r="I29" s="86"/>
-      <c r="J29" s="86"/>
-      <c r="K29" s="86"/>
-      <c r="L29" s="88"/>
-      <c r="M29" s="91" t="s">
+      <c r="H29" s="88"/>
+      <c r="I29" s="88"/>
+      <c r="J29" s="88"/>
+      <c r="K29" s="88"/>
+      <c r="L29" s="90"/>
+      <c r="M29" s="93" t="s">
         <v>84</v>
       </c>
-      <c r="N29" s="86"/>
-      <c r="O29" s="86"/>
-      <c r="P29" s="86"/>
-      <c r="Q29" s="88"/>
+      <c r="N29" s="88"/>
+      <c r="O29" s="88"/>
+      <c r="P29" s="88"/>
+      <c r="Q29" s="90"/>
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A30" s="92"/>
-      <c r="B30" s="93"/>
-      <c r="C30" s="93"/>
-      <c r="D30" s="93"/>
-      <c r="E30" s="93"/>
-      <c r="F30" s="93"/>
-      <c r="G30" s="93"/>
-      <c r="H30" s="93"/>
-      <c r="I30" s="93"/>
-      <c r="J30" s="93"/>
-      <c r="K30" s="93"/>
-      <c r="L30" s="93"/>
-      <c r="M30" s="102"/>
-      <c r="Q30" s="149"/>
+      <c r="A30" s="94"/>
+      <c r="B30" s="95"/>
+      <c r="C30" s="95"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="95"/>
+      <c r="F30" s="95"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="95"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="95"/>
+      <c r="K30" s="95"/>
+      <c r="L30" s="95"/>
+      <c r="M30" s="104"/>
+      <c r="Q30" s="151"/>
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A31" s="150" t="s">
+      <c r="A31" s="152" t="s">
         <v>85</v>
       </c>
-      <c r="B31" s="84"/>
-      <c r="C31" s="151"/>
-      <c r="D31" s="84"/>
-      <c r="E31" s="84"/>
-      <c r="F31" s="84"/>
-      <c r="G31" s="84"/>
-      <c r="H31" s="152"/>
-      <c r="I31" s="152"/>
-      <c r="J31" s="151" t="s">
+      <c r="B31" s="86"/>
+      <c r="C31" s="153"/>
+      <c r="D31" s="86"/>
+      <c r="E31" s="86"/>
+      <c r="F31" s="86"/>
+      <c r="G31" s="86"/>
+      <c r="H31" s="154"/>
+      <c r="I31" s="154"/>
+      <c r="J31" s="153" t="s">
         <v>86</v>
       </c>
-      <c r="K31" s="84"/>
-      <c r="L31" s="152"/>
-      <c r="M31" s="108"/>
-      <c r="N31" s="84"/>
-      <c r="O31" s="84"/>
-      <c r="P31" s="84"/>
-      <c r="Q31" s="103"/>
+      <c r="K31" s="86"/>
+      <c r="L31" s="154"/>
+      <c r="M31" s="110"/>
+      <c r="N31" s="86"/>
+      <c r="O31" s="86"/>
+      <c r="P31" s="86"/>
+      <c r="Q31" s="105"/>
     </row>
     <row r="32" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A32" s="153" t="s">
+      <c r="A32" s="155" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="86"/>
-      <c r="C32" s="86"/>
-      <c r="D32" s="86"/>
-      <c r="E32" s="86"/>
-      <c r="F32" s="86"/>
-      <c r="G32" s="86"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="86"/>
-      <c r="J32" s="86"/>
-      <c r="K32" s="86"/>
-      <c r="L32" s="86"/>
-      <c r="M32" s="86"/>
-      <c r="N32" s="86"/>
-      <c r="O32" s="86"/>
-      <c r="P32" s="86"/>
-      <c r="Q32" s="86"/>
+      <c r="B32" s="88"/>
+      <c r="C32" s="88"/>
+      <c r="D32" s="88"/>
+      <c r="E32" s="88"/>
+      <c r="F32" s="88"/>
+      <c r="G32" s="88"/>
+      <c r="H32" s="88"/>
+      <c r="I32" s="88"/>
+      <c r="J32" s="88"/>
+      <c r="K32" s="88"/>
+      <c r="L32" s="88"/>
+      <c r="M32" s="88"/>
+      <c r="N32" s="88"/>
+      <c r="O32" s="88"/>
+      <c r="P32" s="88"/>
+      <c r="Q32" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="99">
@@ -3381,7 +3398,7 @@
       <c r="A1" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="51" t="s">
         <v>89</v>
       </c>
       <c r="C1" s="4"/>
@@ -3437,14 +3454,14 @@
       <c r="G5" s="5"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:7">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="52" t="s">
         <v>97</v>
       </c>
       <c r="B6" s="7"/>
       <c r="G6" s="8"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:7">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="53" t="s">
         <v>98</v>
       </c>
       <c r="B7" s="10"/>
@@ -3455,257 +3472,257 @@
       <c r="G7" s="12"/>
     </row>
     <row r="8" ht="24.95" customHeight="1" spans="1:7">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="54" t="s">
         <v>99</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="B8" s="55" t="s">
         <v>100</v>
       </c>
       <c r="C8" s="17"/>
-      <c r="D8" s="53" t="s">
+      <c r="D8" s="55" t="s">
         <v>101</v>
       </c>
       <c r="E8" s="17"/>
-      <c r="F8" s="54" t="s">
+      <c r="F8" s="56" t="s">
         <v>102</v>
       </c>
       <c r="G8" s="17"/>
     </row>
     <row r="9" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A9" s="55"/>
-      <c r="B9" s="56"/>
-      <c r="C9" s="57" t="s">
+      <c r="A9" s="57"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="59" t="s">
         <v>103</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="58" t="s">
+      <c r="F9" s="60" t="s">
         <v>104</v>
       </c>
       <c r="G9" s="5"/>
     </row>
     <row r="10" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="61" t="s">
         <v>105</v>
       </c>
-      <c r="B10" s="60" t="s">
+      <c r="B10" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="61" t="s">
+      <c r="C10" s="63" t="s">
         <v>107</v>
       </c>
-      <c r="D10" s="60" t="s">
+      <c r="D10" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="61" t="s">
+      <c r="E10" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="60" t="s">
+      <c r="F10" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="G10" s="62" t="s">
+      <c r="G10" s="64" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="11" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A11" s="31"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="34"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="35"/>
     </row>
     <row r="12" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A12" s="63"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="34"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="35"/>
     </row>
     <row r="13" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A13" s="31"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="34"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="35"/>
     </row>
     <row r="14" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A14" s="31"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="34"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="35"/>
     </row>
     <row r="15" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A15" s="31"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="34"/>
+      <c r="A15" s="32"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="35"/>
     </row>
     <row r="16" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A16" s="35"/>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="38"/>
+      <c r="A16" s="36"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="39"/>
     </row>
     <row r="17" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="65" t="s">
+      <c r="B17" s="67"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="67" t="s">
         <v>104</v>
       </c>
-      <c r="G17" s="67" t="s">
+      <c r="G17" s="69" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="18" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A18" s="68" t="s">
+      <c r="A18" s="70" t="s">
         <v>111</v>
       </c>
       <c r="G18" s="8"/>
     </row>
     <row r="19" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A19" s="68" t="s">
+      <c r="A19" s="70" t="s">
         <v>112</v>
       </c>
       <c r="G19" s="8"/>
     </row>
     <row r="20" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A20" s="69" t="s">
+      <c r="A20" s="71" t="s">
         <v>113</v>
       </c>
-      <c r="B20" s="70"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="71"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="72"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="73"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="72"/>
-      <c r="B21" s="70"/>
-      <c r="C21" s="70"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="71"/>
+      <c r="A21" s="74"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="73"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="72"/>
-      <c r="B22" s="70"/>
-      <c r="C22" s="70"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="71"/>
+      <c r="A22" s="74"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="73"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="72"/>
-      <c r="B23" s="70"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="71"/>
+      <c r="A23" s="74"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="73"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="72"/>
-      <c r="B24" s="70"/>
-      <c r="C24" s="70"/>
-      <c r="D24" s="70"/>
-      <c r="E24" s="70"/>
-      <c r="F24" s="70"/>
-      <c r="G24" s="71"/>
+      <c r="A24" s="74"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="73"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="72"/>
-      <c r="B25" s="70"/>
-      <c r="C25" s="70"/>
-      <c r="D25" s="70"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="70"/>
-      <c r="G25" s="71"/>
+      <c r="A25" s="74"/>
+      <c r="B25" s="72"/>
+      <c r="C25" s="72"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="72"/>
+      <c r="G25" s="73"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="72"/>
-      <c r="B26" s="70"/>
-      <c r="C26" s="70"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="71"/>
+      <c r="A26" s="74"/>
+      <c r="B26" s="72"/>
+      <c r="C26" s="72"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="72"/>
+      <c r="G26" s="73"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="72"/>
-      <c r="B27" s="70"/>
-      <c r="C27" s="70"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="70"/>
-      <c r="F27" s="70"/>
-      <c r="G27" s="71"/>
+      <c r="A27" s="74"/>
+      <c r="B27" s="72"/>
+      <c r="C27" s="72"/>
+      <c r="D27" s="72"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="72"/>
+      <c r="G27" s="73"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="72"/>
-      <c r="B28" s="70"/>
-      <c r="C28" s="70"/>
-      <c r="D28" s="70"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="70"/>
-      <c r="G28" s="71"/>
+      <c r="A28" s="74"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
+      <c r="G28" s="73"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="72"/>
-      <c r="B29" s="70"/>
-      <c r="C29" s="70"/>
-      <c r="D29" s="70"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="70"/>
-      <c r="G29" s="71"/>
+      <c r="A29" s="74"/>
+      <c r="B29" s="72"/>
+      <c r="C29" s="72"/>
+      <c r="D29" s="72"/>
+      <c r="E29" s="72"/>
+      <c r="F29" s="72"/>
+      <c r="G29" s="73"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="72"/>
-      <c r="B30" s="70"/>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="70"/>
-      <c r="G30" s="71"/>
+      <c r="A30" s="74"/>
+      <c r="B30" s="72"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="72"/>
+      <c r="G30" s="73"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="72"/>
-      <c r="B31" s="70"/>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="71"/>
+      <c r="A31" s="74"/>
+      <c r="B31" s="72"/>
+      <c r="C31" s="72"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="72"/>
+      <c r="F31" s="72"/>
+      <c r="G31" s="73"/>
     </row>
     <row r="32" ht="64" customHeight="1" spans="1:7">
-      <c r="A32" s="73"/>
-      <c r="B32" s="74"/>
-      <c r="C32" s="74"/>
-      <c r="D32" s="74"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="75"/>
+      <c r="A32" s="75"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="76"/>
+      <c r="D32" s="76"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -3901,152 +3918,152 @@
       <c r="I9" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="J9" s="29" t="s">
+      <c r="J9" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="K9" s="30" t="s">
+      <c r="K9" s="31" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="10" ht="21.95" customHeight="1" spans="1:16">
-      <c r="A10" s="31"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="34"/>
+      <c r="A10" s="32"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="35"/>
     </row>
     <row r="11" ht="21.95" customHeight="1" spans="1:16">
-      <c r="A11" s="31"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="34"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="35"/>
     </row>
     <row r="12" ht="21.95" customHeight="1" spans="1:16">
-      <c r="A12" s="31"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="34"/>
+      <c r="A12" s="32"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="35"/>
     </row>
     <row r="13" ht="21.95" customHeight="1" spans="1:16">
-      <c r="A13" s="31"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="34"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="35"/>
     </row>
     <row r="14" ht="21.95" customHeight="1" spans="1:16">
-      <c r="A14" s="31"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="34"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="35"/>
     </row>
     <row r="15" ht="21.95" customHeight="1" spans="1:16">
-      <c r="A15" s="31"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="34"/>
+      <c r="A15" s="32"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="35"/>
     </row>
     <row r="16" ht="21.95" customHeight="1" spans="1:16">
-      <c r="A16" s="35"/>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="38"/>
+      <c r="A16" s="36"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="39"/>
     </row>
     <row r="17" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="42" t="s">
+      <c r="B17" s="41"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="43" t="s">
         <v>44</v>
       </c>
       <c r="E17" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="F17" s="43" t="s">
+      <c r="F17" s="44" t="s">
         <v>45</v>
       </c>
       <c r="G17" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="H17" s="43" t="s">
+      <c r="H17" s="44" t="s">
         <v>46</v>
       </c>
       <c r="I17" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="J17" s="43" t="s">
+      <c r="J17" s="45" t="s">
         <v>132</v>
       </c>
-      <c r="K17" s="44" t="s">
+      <c r="K17" s="46" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="18" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="47" t="s">
         <v>134</v>
       </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="47"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="49"/>
     </row>
     <row r="19" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>135</v>
       </c>
       <c r="K19" s="8"/>
